--- a/day-3/day-3.xlsx
+++ b/day-3/day-3.xlsx
@@ -20,16 +20,344 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="53">
+  <si>
+    <t xml:space="preserve">1. SUM() để tính tổng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. AVERAGE() để tính trung bình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. COUNT() để đếm số, nghĩa là cell đó phải kiểu Number hoặc là Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. COUNTA() để đếm ô không trống, nghĩa là bất kì kiểu dữ liệu nào chỉ cần không trống (blank)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. MIN() là tìm giá trị nhỏ nhất, MAX() là tìm giá trị lớn nhất</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. SUMIF() tính tổng theo điều kiện</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMIF(     range,     criteria,     sum_range )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. COUNTIF() là đếm số cell thỏa mãn điều kiện</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COUNTIF(     range,     criteria )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. SUMIFS là tính tổng thỏa mãn nhiều điều kiện</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMIFS(     sum_range,     criteria_range1, criteria1,     criteria_range2, criteria2,     ... )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. COUNTIFS là đếm thỏa mãn nhiều điều kiện</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COUNTIFS(     B2:B8,"Laptop",     C2:C8,"North" )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laptop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mouse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keyboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viết công thức tính:      Tổng Quantity </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">`</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD62E4E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">= SUM(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">D2:D8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD62E4E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viết công thức tính:      Tổng Revenue </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD62E4E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">`</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD62E4E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">=SUMPRODUCT(D2:D8,E2:E8)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viết công thức tính:      Revenue trung bình của tất cả các dòng </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">`</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD62E4E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">=SUMPRODUCT(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">D2:D8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD62E4E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">E2:E8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD62E4E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)/COUNT(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">D2:D8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD62E4E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viết công thức:      Có bao nhiêu dòng có Quantity? </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD62E4E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">`</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD62E4E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">=COUNT(D2:D8)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viết công thức:      Có bao nhiêu dòng thuộc Region = South?  </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD62E4E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">`</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFD62E4E"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">=COUNTIF(C2:C8, "South")</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viết công thức:      Tổng Revenue của Region = South </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viết công thức:      Tổng Revenue của Product = Laptop và Region = North </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Task 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager hỏi:      "Có bao nhiêu order ở South?"  
+Bạn có dùng ngay: excel=COUNTIF(C2:C8,"South")  không?  
+Nếu không, giải thích tại sao.  Câu 8 liên kết trực tiếp với bài COUNT vs COUNT(DISTINCT) và granularity hôm Day 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ở dataset này mỗi dòng là 1 order rồi nên không cần lo lắng gì cứ count bình thường thôi không cần distnct</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -45,6 +373,60 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC9211E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFD62E4E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <u val="single"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFD62E4E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -89,9 +471,57 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -103,6 +533,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FFD62E4E"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FFC9211E"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -111,9 +601,67 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -129,9 +677,292 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <f aca="false">D2*E2</f>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <f aca="false">D3*E3</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <f aca="false">D4*E4</f>
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <f aca="false">D5*E5</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <f aca="false">D6*E6</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <f aca="false">D7*E7</f>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <f aca="false">D8*E8</f>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <f aca="false"> SUM(D2:D8)</f>
+        <v>11</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <f aca="false">SUMPRODUCT(D2:D8,E2:E8)</f>
+        <v>66500</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" s="0" t="n">
+        <f aca="false">SUM(F2:F8)</f>
+        <v>66500</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <f aca="false">SUMPRODUCT(D2:D8,E2:E8)/COUNT(D2:D8)</f>
+        <v>9500</v>
+      </c>
+      <c r="H13" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <f aca="false">COUNT(D2:D8)</f>
+        <v>7</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <f aca="false">COUNTIF(C2:C8, "South")</f>
+        <v>4</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <f aca="false">SUMIF(C2:C8, "South", F2:F8)</f>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="0" t="n">
+        <f aca="false">SUMIFS(F2:F8, B2:B8, "Laptop", C2:C8, "North")</f>
+        <v>62000</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="35.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
